--- a/artfynd/A 30415-2026 artfynd.xlsx
+++ b/artfynd/A 30415-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,1090 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135311057</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>467747</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7096220</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135311058</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>467728</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7096219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135311059</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>467707</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7096210</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135311060</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>467694</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7096204</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135311061</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>467673</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7096206</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135311065</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80413</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>467666</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7096164</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135311066</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80413</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>467662</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7096161</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135311063</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>467676</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7096191</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135311062</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>467663</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7096195</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135311064</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>467671</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7096164</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30415-2026 artfynd.xlsx
+++ b/artfynd/A 30415-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/883466</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311057</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311058</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311059</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311060</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311061</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311065</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311066</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311063</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311062</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1863,8 +1918,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311064</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30415-2026 artfynd.xlsx
+++ b/artfynd/A 30415-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135311057</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135311058</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135311059</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135311060</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135311061</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135311065</v>
       </c>
       <c r="B8" t="n">
-        <v>80413</v>
+        <v>80451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135311066</v>
       </c>
       <c r="B9" t="n">
-        <v>80413</v>
+        <v>80451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135311063</v>
       </c>
       <c r="B10" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135311062</v>
       </c>
       <c r="B11" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>135311064</v>
       </c>
       <c r="B12" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30415-2026 artfynd.xlsx
+++ b/artfynd/A 30415-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135311057</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135311058</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135311059</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135311060</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135311061</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135311065</v>
       </c>
       <c r="B8" t="n">
-        <v>80451</v>
+        <v>80478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135311066</v>
       </c>
       <c r="B9" t="n">
-        <v>80451</v>
+        <v>80478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135311063</v>
       </c>
       <c r="B10" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135311062</v>
       </c>
       <c r="B11" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>135311064</v>
       </c>
       <c r="B12" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 30415-2026 artfynd.xlsx
+++ b/artfynd/A 30415-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,9 +790,1153 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135311057</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>467747</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7096220</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311057</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135311058</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>467728</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7096219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311058</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135311059</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>467707</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7096210</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311059</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135311060</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>467694</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7096204</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311060</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135311061</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>467673</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7096206</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311061</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135311065</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80481</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>467666</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7096164</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311065</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135311066</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80481</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>467662</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7096161</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311066</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135311063</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>467676</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7096191</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311063</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135311062</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>467663</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7096195</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311062</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135311064</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rörtjärnen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>467671</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7096164</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135311064</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30415-2026 artfynd.xlsx
+++ b/artfynd/A 30415-2026 artfynd.xlsx
@@ -1579,7 +1579,7 @@
         <v>135311063</v>
       </c>
       <c r="B10" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135311062</v>
       </c>
       <c r="B11" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>135311064</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
